--- a/research/traditional_assets/database/data/greece/greece_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_brokerage_investment_banking.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0455</v>
+        <v>0.195</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.586</v>
+        <v>2.87</v>
       </c>
       <c r="L2">
-        <v>0.03005128205128205</v>
+        <v>0.1066914498141264</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,61 +630,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.355</v>
+        <v>0.825</v>
       </c>
       <c r="V2">
-        <v>0.03169642857142857</v>
+        <v>0.02291666666666667</v>
       </c>
       <c r="W2">
-        <v>0.1195918367346939</v>
+        <v>0.4991304347826087</v>
       </c>
       <c r="X2">
-        <v>0.08507038909916539</v>
+        <v>0.1022476762042863</v>
       </c>
       <c r="Y2">
-        <v>0.03452144763552847</v>
+        <v>0.3968827585783224</v>
       </c>
       <c r="Z2">
-        <v>0.8703025975185217</v>
+        <v>1.299830877023435</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06300076007556259</v>
+        <v>0.09875153220994534</v>
       </c>
       <c r="AC2">
-        <v>-0.06300076007556259</v>
+        <v>-0.09875153220994534</v>
       </c>
       <c r="AD2">
-        <v>15.3</v>
+        <v>6.78</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.3</v>
+        <v>6.78</v>
       </c>
       <c r="AG2">
-        <v>14.945</v>
+        <v>5.955</v>
       </c>
       <c r="AH2">
-        <v>0.5773584905660377</v>
+        <v>0.1584852734922861</v>
       </c>
       <c r="AI2">
-        <v>0.7268408551068883</v>
+        <v>0.4584178498985801</v>
       </c>
       <c r="AJ2">
-        <v>0.571619812583668</v>
+        <v>0.1419377904898105</v>
       </c>
       <c r="AK2">
-        <v>0.7221551099299348</v>
+        <v>0.4264232008592911</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.04</v>
+        <v>-0.142</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0455</v>
+        <v>0.195</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0.586</v>
+        <v>2.87</v>
       </c>
       <c r="L3">
-        <v>0.03005128205128205</v>
+        <v>0.1066914498141264</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,61 +749,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.355</v>
+        <v>0.825</v>
       </c>
       <c r="V3">
-        <v>0.03169642857142857</v>
+        <v>0.02291666666666667</v>
       </c>
       <c r="W3">
-        <v>0.1195918367346939</v>
+        <v>0.4991304347826087</v>
       </c>
       <c r="X3">
-        <v>0.08507038909916539</v>
+        <v>0.1022476762042863</v>
       </c>
       <c r="Y3">
-        <v>0.03452144763552847</v>
+        <v>0.3968827585783224</v>
       </c>
       <c r="Z3">
-        <v>0.8703025975185217</v>
+        <v>1.299830877023435</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06300076007556259</v>
+        <v>0.09875153220994534</v>
       </c>
       <c r="AC3">
-        <v>-0.06300076007556259</v>
+        <v>-0.09875153220994534</v>
       </c>
       <c r="AD3">
-        <v>15.3</v>
+        <v>6.78</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.3</v>
+        <v>6.78</v>
       </c>
       <c r="AG3">
-        <v>14.945</v>
+        <v>5.955</v>
       </c>
       <c r="AH3">
-        <v>0.5773584905660377</v>
+        <v>0.1584852734922861</v>
       </c>
       <c r="AI3">
-        <v>0.7268408551068883</v>
+        <v>0.4584178498985801</v>
       </c>
       <c r="AJ3">
-        <v>0.571619812583668</v>
+        <v>0.1419377904898105</v>
       </c>
       <c r="AK3">
-        <v>0.7221551099299348</v>
+        <v>0.4264232008592911</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.04</v>
+        <v>-0.142</v>
       </c>
       <c r="AQ3">
         <v>-0</v>

--- a/research/traditional_assets/database/data/greece/greece_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_brokerage_investment_banking.xlsx
@@ -588,7 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.195</v>
+        <v>0.104</v>
+      </c>
+      <c r="E2">
+        <v>0.551</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2.87</v>
+        <v>1.53</v>
       </c>
       <c r="L2">
-        <v>0.1066914498141264</v>
+        <v>0.06710526315789474</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,61 +633,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.825</v>
+        <v>0.583</v>
       </c>
       <c r="V2">
-        <v>0.02291666666666667</v>
+        <v>0.008701492537313432</v>
       </c>
       <c r="W2">
-        <v>0.4991304347826087</v>
+        <v>0.1910112359550562</v>
       </c>
       <c r="X2">
-        <v>0.1022476762042863</v>
+        <v>0.0752133942953962</v>
       </c>
       <c r="Y2">
-        <v>0.3968827585783224</v>
+        <v>0.11579784165966</v>
       </c>
       <c r="Z2">
-        <v>1.299830877023435</v>
+        <v>1.63265306122449</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09875153220994534</v>
+        <v>0.07337465089335007</v>
       </c>
       <c r="AC2">
-        <v>-0.09875153220994534</v>
+        <v>-0.07337465089335007</v>
       </c>
       <c r="AD2">
-        <v>6.78</v>
+        <v>11.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.78</v>
+        <v>11.9</v>
       </c>
       <c r="AG2">
-        <v>5.955</v>
+        <v>11.317</v>
       </c>
       <c r="AH2">
-        <v>0.1584852734922861</v>
+        <v>0.1508238276299113</v>
       </c>
       <c r="AI2">
-        <v>0.4584178498985801</v>
+        <v>0.5456212746446584</v>
       </c>
       <c r="AJ2">
-        <v>0.1419377904898105</v>
+        <v>0.144502470727939</v>
       </c>
       <c r="AK2">
-        <v>0.4264232008592911</v>
+        <v>0.5331417534272389</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.142</v>
+        <v>-0.095</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -707,7 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.195</v>
+        <v>0.104</v>
+      </c>
+      <c r="E3">
+        <v>0.551</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2.87</v>
+        <v>1.53</v>
       </c>
       <c r="L3">
-        <v>0.1066914498141264</v>
+        <v>0.06710526315789474</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,61 +755,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.825</v>
+        <v>0.583</v>
       </c>
       <c r="V3">
-        <v>0.02291666666666667</v>
+        <v>0.008701492537313432</v>
       </c>
       <c r="W3">
-        <v>0.4991304347826087</v>
+        <v>0.1910112359550562</v>
       </c>
       <c r="X3">
-        <v>0.1022476762042863</v>
+        <v>0.0752133942953962</v>
       </c>
       <c r="Y3">
-        <v>0.3968827585783224</v>
+        <v>0.11579784165966</v>
       </c>
       <c r="Z3">
-        <v>1.299830877023435</v>
+        <v>1.63265306122449</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.09875153220994534</v>
+        <v>0.07337465089335007</v>
       </c>
       <c r="AC3">
-        <v>-0.09875153220994534</v>
+        <v>-0.07337465089335007</v>
       </c>
       <c r="AD3">
-        <v>6.78</v>
+        <v>11.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.78</v>
+        <v>11.9</v>
       </c>
       <c r="AG3">
-        <v>5.955</v>
+        <v>11.317</v>
       </c>
       <c r="AH3">
-        <v>0.1584852734922861</v>
+        <v>0.1508238276299113</v>
       </c>
       <c r="AI3">
-        <v>0.4584178498985801</v>
+        <v>0.5456212746446584</v>
       </c>
       <c r="AJ3">
-        <v>0.1419377904898105</v>
+        <v>0.144502470727939</v>
       </c>
       <c r="AK3">
-        <v>0.4264232008592911</v>
+        <v>0.5331417534272389</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.142</v>
+        <v>-0.095</v>
       </c>
       <c r="AQ3">
         <v>-0</v>
